--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N71_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N71_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.08012784032872</v>
+        <v>2.288020774053418</v>
       </c>
       <c r="D2" t="n">
-        <v>14.21002878657867</v>
+        <v>2.309129677819034</v>
       </c>
       <c r="E2" t="n">
-        <v>7.251950649106088</v>
+        <v>1.17844198047974</v>
       </c>
       <c r="F2" t="n">
-        <v>7.693002201412868</v>
+        <v>1.250112857729591</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.05415000662375</v>
+        <v>1.958799376076359</v>
       </c>
       <c r="D3" t="n">
-        <v>8.921051919932809</v>
+        <v>1.449670936989082</v>
       </c>
       <c r="E3" t="n">
-        <v>7.251950649106088</v>
+        <v>1.17844198047974</v>
       </c>
       <c r="F3" t="n">
-        <v>7.693002201412868</v>
+        <v>1.250112857729591</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.78892917891868</v>
+        <v>2.240700991574286</v>
       </c>
       <c r="D4" t="n">
-        <v>14.51375059310184</v>
+        <v>2.35848447137905</v>
       </c>
       <c r="E4" t="n">
-        <v>7.251950649106088</v>
+        <v>1.17844198047974</v>
       </c>
       <c r="F4" t="n">
-        <v>7.693002201412868</v>
+        <v>1.250112857729591</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.95960399869673</v>
+        <v>4.86843564978822</v>
       </c>
       <c r="D5" t="n">
-        <v>29.5560347124794</v>
+        <v>4.802855640777903</v>
       </c>
       <c r="E5" t="n">
-        <v>7.251950649106088</v>
+        <v>1.17844198047974</v>
       </c>
       <c r="F5" t="n">
-        <v>7.693002201412868</v>
+        <v>1.250112857729591</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
